--- a/SGC-CKN/Excel/8d730efd-c9ce-4f02-ada5-6d6b0bd09d4a_Nhà_hát_P_326_D1200_28-03-2026.xlsx
+++ b/SGC-CKN/Excel/8d730efd-c9ce-4f02-ada5-6d6b0bd09d4a_Nhà_hát_P_326_D1200_28-03-2026.xlsx
@@ -153,7 +153,7 @@
   </si>
   <si>
     <t xml:space="preserve">23:15
-28/03/2026</t>
+27/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -331,12 +331,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF7C2D12"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -358,6 +352,12 @@
     </font>
     <font>
       <color rgb="FF312E81"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -438,11 +438,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
       </patternFill>
     </fill>
@@ -464,6 +459,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC7D2FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -636,6 +636,12 @@
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -674,12 +680,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1454,155 +1454,155 @@
         <v>-34</v>
       </c>
       <c r="H16" s="22">
-        <v>24.5</v>
+        <v>0.5</v>
       </c>
       <c r="I16" s="22">
         <v>2.8</v>
       </c>
-      <c r="J16" s="25">
-        <v>0.11</v>
+      <c r="J16" s="8">
+        <v>5.6</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="27" t="s">
+      <c r="B17" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <v>-34</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <v>-37.3</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>2.25</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="25">
         <v>3.3</v>
       </c>
       <c r="J17" s="12">
         <v>1.47</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="26" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="30" t="s">
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>-37.3</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>-44.2</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>5.25</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="28">
         <v>6.9</v>
       </c>
       <c r="J18" s="12">
         <v>1.31</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="29" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="33" t="s">
+      <c r="B19" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="31">
         <v>-44.2</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="31">
         <v>-57.1</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="31">
         <v>1.58</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="31">
         <v>12.9</v>
       </c>
       <c r="J19" s="8">
         <v>8.15</v>
       </c>
-      <c r="K19" s="33" t="s">
+      <c r="K19" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="36" t="s">
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="E20" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="34">
         <v>-57.1</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="34">
         <v>-61.4</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="34">
         <v>0.92</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <v>4.3</v>
       </c>
       <c r="J20" s="12">
         <v>4.69</v>
       </c>
-      <c r="K20" s="36" t="s">
+      <c r="K20" s="35" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1642,37 +1642,37 @@
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="39" t="s">
+      <c r="B22" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="37">
         <v>-64.6</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22" s="37">
         <v>-65.8</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="37">
         <v>0.5</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22" s="37">
         <v>1.2</v>
       </c>
       <c r="J22" s="12">
         <v>2.4</v>
       </c>
-      <c r="K22" s="39" t="s">
+      <c r="K22" s="38" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       <c r="I24" s="9">
         <v>0.25</v>
       </c>
-      <c r="J24" s="25">
+      <c r="J24" s="40">
         <v>0.06</v>
       </c>
       <c r="K24" s="10" t="s">
@@ -2046,38 +2046,38 @@
         <v>-34</v>
       </c>
       <c r="G7" s="22">
-        <v>24.5</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="22">
         <v>2.8</v>
       </c>
-      <c r="I7" s="25">
-        <v>0.11</v>
+      <c r="I7" s="8">
+        <v>5.6</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>-34</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="25">
         <v>-37.3</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25">
         <v>2.25</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>3.3</v>
       </c>
       <c r="I8" s="12">
@@ -2085,28 +2085,28 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="30" t="s">
+      <c r="B9" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>-37.3</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>-44.2</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>5.25</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>6.9</v>
       </c>
       <c r="I9" s="12">
@@ -2114,28 +2114,28 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="33" t="s">
+      <c r="B10" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="31">
         <v>1</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="31">
         <v>-44.2</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="31">
         <v>-57.1</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="31">
         <v>1.58</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <v>12.9</v>
       </c>
       <c r="I10" s="8">
@@ -2143,28 +2143,28 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="36" t="s">
+      <c r="B11" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <v>-57.1</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <v>-61.4</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="34">
         <v>0.92</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="34">
         <v>4.3</v>
       </c>
       <c r="I11" s="12">
@@ -2201,28 +2201,28 @@
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="38">
+      <c r="A13" s="37">
         <v>12</v>
       </c>
-      <c r="B13" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="39" t="s">
+      <c r="B13" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="37">
         <v>1</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="37">
         <v>-64.6</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="37">
         <v>-65.8</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="37">
         <v>0.5</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="37">
         <v>1.2</v>
       </c>
       <c r="I13" s="12">
@@ -2283,7 +2283,7 @@
       <c r="H15" s="9">
         <v>0.25</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="40">
         <v>0.06</v>
       </c>
     </row>
@@ -2307,13 +2307,13 @@
         <v>-73.45</v>
       </c>
       <c r="G16" s="43">
-        <v>42.63</v>
+        <v>18.63</v>
       </c>
       <c r="H16" s="43">
         <v>73.45</v>
       </c>
       <c r="I16" s="43">
-        <v>1.72</v>
+        <v>3.94</v>
       </c>
     </row>
   </sheetData>
